--- a/mufrodat.xlsx
+++ b/mufrodat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASATIDZ\Zen\bahasa-terbaru\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA18E95D-71F7-4E35-BE3D-1A9E61D63247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B3C17C-D6C6-449F-8962-35855993AFE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mufrodat" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="putri" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">putra!$A$1:$B$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">putra!$A$1:$B$32</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">putri!$A$1:$B$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="146">
   <si>
     <t>Nomor</t>
   </si>
@@ -360,9 +360,6 @@
   </si>
   <si>
     <t>Muhammad Nizam Ghifari</t>
-  </si>
-  <si>
-    <t>Muhammad Nur Riski</t>
   </si>
   <si>
     <t>Nadil Al Fayyadh</t>
@@ -561,7 +558,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -581,26 +578,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -907,7 +901,7 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+      <c r="A2" s="11">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -918,7 +912,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
+      <c r="A3" s="11"/>
       <c r="B3" s="5" t="s">
         <v>4</v>
       </c>
@@ -927,7 +921,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
+      <c r="A4" s="11"/>
       <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
@@ -936,7 +930,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
+      <c r="A5" s="11"/>
       <c r="B5" s="5" t="s">
         <v>6</v>
       </c>
@@ -945,7 +939,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
+      <c r="A6" s="11"/>
       <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
@@ -954,7 +948,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="A7" s="12">
         <f>A2+1</f>
         <v>2</v>
       </c>
@@ -966,7 +960,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
+      <c r="A8" s="12"/>
       <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
@@ -975,7 +969,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
+      <c r="A9" s="12"/>
       <c r="B9" s="3" t="s">
         <v>10</v>
       </c>
@@ -984,7 +978,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
+      <c r="A10" s="12"/>
       <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
@@ -993,7 +987,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
+      <c r="A11" s="12"/>
       <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
@@ -1002,7 +996,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+      <c r="A12" s="11">
         <f t="shared" ref="A12" si="0">A7+1</f>
         <v>3</v>
       </c>
@@ -1014,7 +1008,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
+      <c r="A13" s="11"/>
       <c r="B13" s="5" t="s">
         <v>14</v>
       </c>
@@ -1023,7 +1017,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
+      <c r="A14" s="11"/>
       <c r="B14" s="5" t="s">
         <v>15</v>
       </c>
@@ -1032,7 +1026,7 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
+      <c r="A15" s="11"/>
       <c r="B15" s="5" t="s">
         <v>16</v>
       </c>
@@ -1041,7 +1035,7 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
+      <c r="A16" s="11"/>
       <c r="B16" s="5" t="s">
         <v>17</v>
       </c>
@@ -1050,7 +1044,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="A17" s="12">
         <f t="shared" ref="A17" si="1">A12+1</f>
         <v>4</v>
       </c>
@@ -1062,7 +1056,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
+      <c r="A18" s="12"/>
       <c r="B18" s="3" t="s">
         <v>19</v>
       </c>
@@ -1071,7 +1065,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
+      <c r="A19" s="12"/>
       <c r="B19" s="3" t="s">
         <v>20</v>
       </c>
@@ -1080,7 +1074,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
+      <c r="A20" s="12"/>
       <c r="B20" s="3" t="s">
         <v>21</v>
       </c>
@@ -1089,7 +1083,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
+      <c r="A21" s="12"/>
       <c r="B21" s="3" t="s">
         <v>22</v>
       </c>
@@ -1098,7 +1092,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
+      <c r="A22" s="11">
         <f t="shared" ref="A22" si="2">A17+1</f>
         <v>5</v>
       </c>
@@ -1110,7 +1104,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
+      <c r="A23" s="11"/>
       <c r="B23" s="5" t="s">
         <v>24</v>
       </c>
@@ -1119,7 +1113,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
+      <c r="A24" s="11"/>
       <c r="B24" s="5" t="s">
         <v>25</v>
       </c>
@@ -1128,7 +1122,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
+      <c r="A25" s="11"/>
       <c r="B25" s="5" t="s">
         <v>26</v>
       </c>
@@ -1137,7 +1131,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
+      <c r="A26" s="11"/>
       <c r="B26" s="5" t="s">
         <v>27</v>
       </c>
@@ -1146,7 +1140,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="A27" s="12">
         <f t="shared" ref="A27" si="3">A22+1</f>
         <v>6</v>
       </c>
@@ -1158,7 +1152,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
+      <c r="A28" s="12"/>
       <c r="B28" s="3" t="s">
         <v>29</v>
       </c>
@@ -1167,7 +1161,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
+      <c r="A29" s="12"/>
       <c r="B29" s="3" t="s">
         <v>30</v>
       </c>
@@ -1176,7 +1170,7 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
+      <c r="A30" s="12"/>
       <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
@@ -1185,7 +1179,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
+      <c r="A31" s="12"/>
       <c r="B31" s="3" t="s">
         <v>32</v>
       </c>
@@ -1194,7 +1188,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="4">
+      <c r="A32" s="11">
         <f t="shared" ref="A32" si="4">A27+1</f>
         <v>7</v>
       </c>
@@ -1206,7 +1200,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
+      <c r="A33" s="11"/>
       <c r="B33" s="5" t="s">
         <v>34</v>
       </c>
@@ -1215,7 +1209,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
+      <c r="A34" s="11"/>
       <c r="B34" s="5" t="s">
         <v>35</v>
       </c>
@@ -1224,7 +1218,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
+      <c r="A35" s="11"/>
       <c r="B35" s="5" t="s">
         <v>36</v>
       </c>
@@ -1233,7 +1227,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
+      <c r="A36" s="11"/>
       <c r="B36" s="5" t="s">
         <v>37</v>
       </c>
@@ -1242,7 +1236,7 @@
       </c>
     </row>
     <row r="37" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+      <c r="A37" s="12">
         <f t="shared" ref="A37" si="5">A32+1</f>
         <v>8</v>
       </c>
@@ -1254,7 +1248,7 @@
       </c>
     </row>
     <row r="38" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
+      <c r="A38" s="12"/>
       <c r="B38" s="3" t="s">
         <v>39</v>
       </c>
@@ -1263,7 +1257,7 @@
       </c>
     </row>
     <row r="39" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
+      <c r="A39" s="12"/>
       <c r="B39" s="3" t="s">
         <v>40</v>
       </c>
@@ -1272,7 +1266,7 @@
       </c>
     </row>
     <row r="40" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
+      <c r="A40" s="12"/>
       <c r="B40" s="3" t="s">
         <v>41</v>
       </c>
@@ -1281,7 +1275,7 @@
       </c>
     </row>
     <row r="41" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2"/>
+      <c r="A41" s="12"/>
       <c r="B41" s="3" t="s">
         <v>42</v>
       </c>
@@ -1290,7 +1284,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="4">
+      <c r="A42" s="11">
         <f t="shared" ref="A42" si="6">A37+1</f>
         <v>9</v>
       </c>
@@ -1302,7 +1296,7 @@
       </c>
     </row>
     <row r="43" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="4"/>
+      <c r="A43" s="11"/>
       <c r="B43" s="5" t="s">
         <v>44</v>
       </c>
@@ -1311,7 +1305,7 @@
       </c>
     </row>
     <row r="44" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="4"/>
+      <c r="A44" s="11"/>
       <c r="B44" s="5" t="s">
         <v>45</v>
       </c>
@@ -1320,7 +1314,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="4"/>
+      <c r="A45" s="11"/>
       <c r="B45" s="5" t="s">
         <v>46</v>
       </c>
@@ -1329,7 +1323,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="4"/>
+      <c r="A46" s="11"/>
       <c r="B46" s="5" t="s">
         <v>47</v>
       </c>
@@ -1360,7 +1354,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="21" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -1373,11 +1367,11 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -1385,7 +1379,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+      <c r="A3" s="4">
         <f>A2+1</f>
         <v>2</v>
       </c>
@@ -1394,7 +1388,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9">
+      <c r="A4" s="4">
         <f t="shared" ref="A4:A10" si="0">A3+1</f>
         <v>3</v>
       </c>
@@ -1403,25 +1397,25 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
+      <c r="A5" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9">
+      <c r="A6" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
+      <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1430,16 +1424,16 @@
       </c>
     </row>
     <row r="8" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9">
+      <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="9" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
+      <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1448,56 +1442,56 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9">
+      <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>107</v>
+      <c r="B10" s="9" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
+      <c r="A11" s="2">
         <v>1</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="10" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
+      <c r="A12" s="2">
         <v>2</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="3" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
+      <c r="A13" s="2">
         <v>3</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="10" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
+      <c r="A14" s="2">
         <v>4</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="10" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
+      <c r="A15" s="2">
         <v>5</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="10" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10">
+      <c r="A16" s="2">
         <v>6</v>
       </c>
       <c r="B16" s="7" t="s">
@@ -1505,7 +1499,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
+      <c r="A17" s="2">
         <v>7</v>
       </c>
       <c r="B17" s="7" t="s">
@@ -1513,31 +1507,31 @@
       </c>
     </row>
     <row r="18" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10">
+      <c r="A18" s="2">
         <v>8</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10">
+      <c r="A19" s="2">
         <v>9</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9">
+      <c r="A20" s="4">
         <v>1</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9">
+      <c r="A21" s="4">
         <v>2</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -1545,7 +1539,7 @@
       </c>
     </row>
     <row r="22" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9">
+      <c r="A22" s="4">
         <v>3</v>
       </c>
       <c r="B22" s="8" t="s">
@@ -1553,7 +1547,7 @@
       </c>
     </row>
     <row r="23" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="9">
+      <c r="A23" s="4">
         <v>4</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -1561,7 +1555,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="9">
+      <c r="A24" s="4">
         <v>5</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -1569,89 +1563,73 @@
       </c>
     </row>
     <row r="25" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="9">
+      <c r="A25" s="4">
         <v>6</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="9">
+      <c r="A26" s="4">
         <v>7</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="9">
+      <c r="A27" s="4">
         <v>8</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="9">
+      <c r="A28" s="4">
         <v>9</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="10">
+      <c r="A29" s="2">
         <v>1</v>
       </c>
-      <c r="B29" s="12" t="s">
-        <v>131</v>
+      <c r="B29" s="10" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="10">
+      <c r="A30" s="2">
         <v>2</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="10">
+      <c r="A31" s="2">
         <v>3</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="10">
+      <c r="A32" s="2">
         <v>4</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="10">
-        <v>5</v>
-      </c>
-      <c r="B33" s="7" t="s">
         <v>141</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="10">
-        <v>6</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>142</v>
       </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1673,11 +1651,11 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -1685,7 +1663,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+      <c r="A3" s="4">
         <f>A2+1</f>
         <v>2</v>
       </c>
@@ -1694,7 +1672,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9">
+      <c r="A4" s="4">
         <f t="shared" ref="A4:A10" si="0">A3+1</f>
         <v>3</v>
       </c>
@@ -1703,25 +1681,25 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
+      <c r="A5" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9">
+      <c r="A6" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
+      <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1730,126 +1708,126 @@
       </c>
     </row>
     <row r="8" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9">
+      <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>108</v>
+      <c r="B8" s="9" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
+      <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9">
+      <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>119</v>
+      <c r="B10" s="9" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
+      <c r="A11" s="2">
         <v>1</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>121</v>
+      <c r="B11" s="10" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
+      <c r="A12" s="2">
         <v>2</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>3</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
+    <row r="14" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>4</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>5</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>6</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>7</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>8</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>1</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>2</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
         <v>3</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
-        <v>4</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
-        <v>5</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10">
-        <v>6</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
-        <v>7</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10">
-        <v>8</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10">
-        <v>9</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9">
-        <v>1</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9">
-        <v>2</v>
-      </c>
-      <c r="B21" s="8" t="s">
+      <c r="B22" s="8" t="s">
         <v>144</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9">
-        <v>3</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>145</v>
       </c>
     </row>
   </sheetData>
